--- a/input_folder/daily_variables/01_04-06-2017_daily_variables.xlsx
+++ b/input_folder/daily_variables/01_04-06-2017_daily_variables.xlsx
@@ -1526,11 +1526,7 @@
           <t>Range (0 - 1000)</t>
         </is>
       </c>
-      <c r="H20" s="42" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="H20" s="42" t="inlineStr"/>
       <c r="I20" s="40" t="n"/>
     </row>
     <row r="21" ht="25.5" customHeight="1">
